--- a/src/testresults/LaptopProducts.xlsx
+++ b/src/testresults/LaptopProducts.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="89">
   <si>
     <t>Product Name</t>
   </si>
@@ -32,118 +32,253 @@
     <t>₹16,490</t>
   </si>
   <si>
+    <t>ASUS ExpertBook P1 (i3 14th Gen) with 1 Yr ADP Intel Core 3 14th Gen 100U - (8 GB/512 GB SSD/Windows 1...</t>
+  </si>
+  <si>
+    <t>₹46,990</t>
+  </si>
+  <si>
+    <t>Acer Aspire 3 Intel Pentium Quad Core N6000 - (12 GB/512 GB SSD/Windows 11 Home) A325-45 Thin and Ligh...</t>
+  </si>
+  <si>
+    <t>₹39,938</t>
+  </si>
+  <si>
+    <t>ASUS Vivobook 15 (2026) with Office 2024 + M365 Basic*, AMD Ryzen 5 Hexa Core 150 - (16 GB/512 GB SSD/...</t>
+  </si>
+  <si>
+    <t>₹58,990</t>
+  </si>
+  <si>
+    <t>ASUS Chromebook CX15 Intel Celeron Dual Core N50 - (4 GB/128 GB EMMC Storage/Chrome OS) CX1505CTA-S702...</t>
+  </si>
+  <si>
+    <t>₹21,990</t>
+  </si>
+  <si>
+    <t>Ultimus APEX Intel Celeron Dual Core - (8 GB/512 GB SSD/Windows 11 Home) NU14U7INC56BN-CS Laptop</t>
+  </si>
+  <si>
+    <t>₹24,699</t>
+  </si>
+  <si>
+    <t>ASUS Expertbook AMD Ryzen 5 Hexa Core 150 - (16 GB/512 GB SSD/Windows 11 Home) PM1403CDA-S60409WS Lapt...</t>
+  </si>
+  <si>
+    <t>₹1,69,990</t>
+  </si>
+  <si>
+    <t>Lenovo IdeaPad Slim 3 Next Gen AI PC WUXGA IPS Copilot + PC with 1Yr ADP Snapdragon X - (16 GB/512 GB ...</t>
+  </si>
+  <si>
+    <t>₹56,990</t>
+  </si>
+  <si>
+    <t>HP 15 (i3 14th Gen) Intel Core 3 100U - (8 GB/512 GB SSD/Windows 11 Home) 15-fd1253TU/ 15-fd1225TU Thi...</t>
+  </si>
+  <si>
+    <t>₹41,838</t>
+  </si>
+  <si>
+    <t>Lenovo Ryzen 5 220 AMD Ryzen 5 Hexa Core 220 - (16 GB/1 TB SSD/Windows 11 Home) 21V0A01SIG Laptop</t>
+  </si>
+  <si>
+    <t>₹77,990</t>
+  </si>
+  <si>
+    <t>Lenovo Ultra 5 225U Intel Core Ultra 5 225U - (16 GB/1 TB SSD/Windows 11 Home) 21SKA0FTIG Laptop</t>
+  </si>
+  <si>
+    <t>₹88,990</t>
+  </si>
+  <si>
+    <t>Acer One 14 AMD Ryzen 3 Quad Core 7320U - (8 GB/256 GB SSD/Windows 11 Home) A114-43 Thin and Light Lap...</t>
+  </si>
+  <si>
+    <t>₹39,990</t>
+  </si>
+  <si>
+    <t>DELL Pro Essential 15 Intel Core 3 14th Gen 100U - (8 GB/512 GB SSD/Ubuntu) PV15250 Thin and Light Lap...</t>
+  </si>
+  <si>
+    <t>₹50,799</t>
+  </si>
+  <si>
+    <t>Jio MediaTek MT8788 - (4 GB/64 GB EMMC Storage/Android 11) NB1112MMBLU Laptop</t>
+  </si>
+  <si>
+    <t>₹14,990</t>
+  </si>
+  <si>
+    <t>ASUS Vivobook 14 (2025) with Office 2024 + M365 Basic*, Backlit Keyboard, Intel Core Ultra 5 225H - (1...</t>
+  </si>
+  <si>
+    <t>₹66,990</t>
+  </si>
+  <si>
+    <t>Lenovo 100e Chromebook Gen 4 MediaTek Kompanio 520 - (4 GB/32 GB EMMC Storage/Chrome OS) 100e Chromebo...</t>
+  </si>
+  <si>
+    <t>₹16,298</t>
+  </si>
+  <si>
+    <t>ASUS TUF Gaming A15 (2025) AMD Ryzen 7 7445HS - (16 GB/512 GB SSD/Windows 11 Home/4 GB Graphics/NVIDIA...</t>
+  </si>
+  <si>
+    <t>₹68,990</t>
+  </si>
+  <si>
+    <t>ASUS Intel Core Ultra 7 - (32 GB/1 TB SSD/Windows 11 Home) P5405CAA-NZ0099WS Laptop</t>
+  </si>
+  <si>
+    <t>₹4,29,990</t>
+  </si>
+  <si>
+    <t>ASUS Chromebook CX14 Intel Celeron Dual Core N4500 - (4 GB/64 GB EMMC Storage/Chrome OS) CX1405CKA-NK0...</t>
+  </si>
+  <si>
+    <t>HP Victus AI AMD Ryzen 7 Octa Core 260 - (24 GB/1 TB SSD/Windows 11 Home/8 GB Graphics/NVIDIA GeForce ...</t>
+  </si>
+  <si>
+    <t>₹1,14,990</t>
+  </si>
+  <si>
+    <t>Lenovo IdeaPad Slim 3 Intel Core i3 13th Gen 1315U - (8 GB/512 GB SSD/Windows 11 Home) IdeaPad Slim 3 ...</t>
+  </si>
+  <si>
+    <t>₹48,490</t>
+  </si>
+  <si>
+    <t>Lenovo IdeaPad Slim 3 AMD Ryzen 7 Octa Core 8840H Office 2024 and Backlit Keyboard AMD Ryzen 7 Octa Co...</t>
+  </si>
+  <si>
+    <t>₹84,490</t>
+  </si>
+  <si>
+    <t>Acer Aspire 3 Intel Celeron Dual Core - (8 GB/256 GB SSD/Windows 11 Home) A311-45 Thin and Light Lapto...</t>
+  </si>
+  <si>
+    <t>₹39,200</t>
+  </si>
+  <si>
+    <t>Lenovo LoQ Intel Core i5 13th Gen 13450HX - (16 GB/512 GB SSD/Windows 11 Home/4 GB Graphics/NVIDIA GeF...</t>
+  </si>
+  <si>
+    <t>₹76,990</t>
+  </si>
+  <si>
+    <t>ASUS TUF Gaming A15 (2026) AMD Ryzen 7 170 - (16 GB/512 GB SSD/Windows 11 Home/4 GB Graphics/NVIDIA Ge...</t>
+  </si>
+  <si>
+    <t>₹75,990</t>
+  </si>
+  <si>
+    <t>Lenovo 100e Chromebook Gen 4 MediaTek MediaTek Kompanio 528 - (4 GB/64 GB EMMC Storage/Chrome OS) 100e...</t>
+  </si>
+  <si>
+    <t>₹22,490</t>
+  </si>
+  <si>
+    <t>ASUS ROG Zephyrus G16 OLED (2026) Intel Core Ultra 9 386H - (32 GB/2 TB SSD/Windows 11 Home/12 GB Grap...</t>
+  </si>
+  <si>
+    <t>₹4,59,990</t>
+  </si>
+  <si>
+    <t>Primebook 2 Pro (2025) in-Built AI MediaTek Helio G99 (MT8781) - (8 GB/128 GB/Android 15) PBG9914128#4...</t>
+  </si>
+  <si>
+    <t>₹25,990</t>
+  </si>
+  <si>
+    <t>HP 14 AI PC Intel Core Ultra 7 155H - (16 GB/1 TB SSD/Windows 11 Home) 14-ep1152TU Thin and Light Lapt...</t>
+  </si>
+  <si>
+    <t>₹79,990</t>
+  </si>
+  <si>
+    <t>HP OMEN AI AMD Ryzen AI 7 Octa Core AI 7 350 - (24 GB/1 TB SSD/Windows 11 Home/8 GB Graphics/NVIDIA Ge...</t>
+  </si>
+  <si>
+    <t>₹1,34,990</t>
+  </si>
+  <si>
+    <t>HP 15 with MSO'2024 AMD Ryzen 3 Quad Core 7320U - (8 GB/512 GB SSD/Windows 11 Home) 15-fc0025AU | 15-f...</t>
+  </si>
+  <si>
+    <t>₹46,700</t>
+  </si>
+  <si>
+    <t>Lenovo IdeaPad Slim 5 WUXGA OLED Full Metal Body with 1Yr ADP Intel Core i5 13th Gen 13420H - (16 GB/5...</t>
+  </si>
+  <si>
+    <t>₹63,999</t>
+  </si>
+  <si>
+    <t>Lenovo IdeaPad Slim 3 WUXGA IPS with 1Yr ADP Intel Core i5 13th Gen 13420H - (16 GB/512 GB SSD/Windows...</t>
+  </si>
+  <si>
     <t>ASUS Vivobook 15 (2025) with Office 2024 + M365 Basic*, Intel Core i3 13th Gen 1315U - (8 GB/512 GB SS...</t>
   </si>
   <si>
     <t>₹40,990</t>
   </si>
   <si>
-    <t>MSI Modern 14 Intel Core i3 13th Gen 1315U - (8 GB/512 GB SSD/Windows 11 Home) Modern 14 C13M-115IN Th...</t>
-  </si>
-  <si>
-    <t>₹39,990</t>
-  </si>
-  <si>
-    <t>Lenovo IdeaPad Slim 3 Intel Core i3 13th Gen 1315U - (8 GB/512 GB SSD/Windows 11 Home) IdeaPad Slim 3 ...</t>
-  </si>
-  <si>
-    <t>₹48,490</t>
-  </si>
-  <si>
-    <t>HP Victus Intel Core i5 13th Gen 13420 H - (16 GB/512 GB SSD/Windows 11 Home/6 GB Graphics/NVIDIA GeFo...</t>
-  </si>
-  <si>
-    <t>₹79,990</t>
-  </si>
-  <si>
-    <t>Samsung Galaxy Book4 Metal Intel Core i5 13th Gen 1335U - (16 GB/512 GB SSD/Windows 11 Home) NP750XGJ ...</t>
-  </si>
-  <si>
-    <t>₹58,990</t>
-  </si>
-  <si>
-    <t>Acer Aspire 5 Intel Core Ultra 5 125H - (16 GB/512 GB SSD/Windows 11 Home) A514-54H Notebook</t>
-  </si>
-  <si>
-    <t>₹89,990</t>
-  </si>
-  <si>
-    <t>ASUS Vivobook 15 (2025) with Office 2024 + M365 Basic* Intel Core i3 13th Gen - (8 GB/512 GB SSD/Windo...</t>
-  </si>
-  <si>
-    <t>ASUS ExpertBook P1 (i3 14th Gen) with 1 Yr ADP Intel Core 3 14th Gen 100U - (8 GB/512 GB SSD/Windows 1...</t>
-  </si>
-  <si>
-    <t>₹46,990</t>
-  </si>
-  <si>
-    <t>HP 15 (i5 14th Gen) Intel Core 5 120U - (16 GB/512 GB SSD/Windows 11 Home) 15-fd0665TU / 15-fd0640TU /...</t>
-  </si>
-  <si>
-    <t>₹64,990</t>
-  </si>
-  <si>
-    <t>ASUS Chromebook CX15 Intel Celeron Dual Core N50 - (4 GB/128 GB EMMC Storage/Chrome OS) CX1505CTA-S702...</t>
-  </si>
-  <si>
-    <t>₹21,990</t>
-  </si>
-  <si>
-    <t>Acer Aspire 3 Intel Pentium Quad Core N6000 - (12 GB/512 GB SSD/Windows 11 Home) A325-45 Thin and Ligh...</t>
-  </si>
-  <si>
-    <t>₹43,990</t>
-  </si>
-  <si>
-    <t>HP 15 with MSO'2024 AMD Ryzen 3 Quad Core 7320U - (8 GB/512 GB SSD/Windows 11 Home) 15-fc0025AU | 15-f...</t>
+    <t>ASUS Vivobook 14 (2026) AI PC with Office 2024 + M365 Basic*, Copilot+ PC Intel Core Ultra 5 325 - (16...</t>
+  </si>
+  <si>
+    <t>₹94,990</t>
+  </si>
+  <si>
+    <t>Lenovo Chromebook 11IJL9 Intel Celeron Dual Core N4500 - (4 GB/64 GB EMMC Storage/Chrome OS) Chromeboo...</t>
   </si>
   <si>
     <t>Samsung Galaxy Book4 Metal Intel Core i7 13th Gen 1355U - (16 GB/512 GB SSD/Windows 11 Home) NP750XGJ-...</t>
   </si>
   <si>
-    <t>₹66,990</t>
+    <t>₹71,990</t>
   </si>
   <si>
     <t>HP 15 Intel Core i5 13th Gen 1335U - (16 GB/512 GB SSD/Windows 11 Home) 15-fd0576TU / 15-fd0467TU Thin...</t>
   </si>
   <si>
-    <t>DELL 15 (2025) Microsoft Office Home 2024 AMD Ryzen 5 Hexa Core 7530U - (16 GB/512 GB SSD/Windows 11 H...</t>
-  </si>
-  <si>
-    <t>₹56,990</t>
-  </si>
-  <si>
-    <t>Lenovo 100e Chromebook Gen 4 MediaTek Kompanio 520 - (4 GB/32 GB EMMC Storage/Chrome OS) 100e Chromebo...</t>
-  </si>
-  <si>
-    <t>₹16,298</t>
-  </si>
-  <si>
-    <t>HP 15s Intel Core i3 11th Gen 1125G4 - (8 GB/512 GB SSD/Windows 11 Home) 15s-fq2629TU Thin and Light L...</t>
-  </si>
-  <si>
-    <t>₹42,990</t>
-  </si>
-  <si>
-    <t>Lenovo IdeaPad Slim 3 Next Gen AI PC WUXGA IPS Copilot + PC with 1Yr ADP Snapdragon X - (16 GB/512 GB ...</t>
-  </si>
-  <si>
-    <t>₹59,990</t>
-  </si>
-  <si>
-    <t>ASUS Chromebook CX14 Intel Celeron Dual Core N4500 - (4 GB/64 GB EMMC Storage/Chrome OS) CX1405CKA-NK0...</t>
-  </si>
-  <si>
-    <t>HP 14 AI PC Intel Core Ultra 7 155H - (16 GB/1 TB SSD/Windows 11 Home) 14-ep1152TU Thin and Light Lapt...</t>
-  </si>
-  <si>
-    <t>₹82,990</t>
-  </si>
-  <si>
-    <t>ASUS Vivobook S14 Flip (2025) with Office 2024 + M365 Basic*, Backlit Keyboard, Intel Core i5 13th Gen...</t>
-  </si>
-  <si>
-    <t>₹63,990</t>
+    <t>ASUS TUF Gaming A15 (2026) AMD Ryzen 7 170 - (16 GB/1 TB SSD/Windows 11 Home/4 GB Graphics/NVIDIA GeFo...</t>
+  </si>
+  <si>
+    <t>₹85,990</t>
+  </si>
+  <si>
+    <t>DELL 15 (Previously Inspiron) AI Powered Intel Core Ultra 5 225H - (8 GB/512 GB SSD/Windows 11 Home) 1...</t>
+  </si>
+  <si>
+    <t>ASUS Vivobook S14 (2025) with Office 2024 + M365 Basic*, Backlit Keyboard, Intel Core i7 13th Gen 1362...</t>
+  </si>
+  <si>
+    <t>₹78,890</t>
+  </si>
+  <si>
+    <t>HP 250R G10 (2025) (i3 14th Gen) Intel Core 3 14th Gen 100U - (8 GB/512 GB SSD/Windows 11 Home) 250R G...</t>
+  </si>
+  <si>
+    <t>Acer Aspire 3 Backlit AMD Ryzen 7 Octa Core 7730U - (16 GB/512 GB SSD/Windows 11 Home) Aspire AS15 - 4...</t>
+  </si>
+  <si>
+    <t>₹55,990</t>
+  </si>
+  <si>
+    <t>Lenovo IdeaPad Slim 3 with 1Yr ADP Intel Core i5 12th Gen 12450H - (16 GB/512 GB SSD/Windows 11 Home) ...</t>
+  </si>
+  <si>
+    <t>ASUS ROG Strix G16 (2026) AMD Ryzen 9 16 Core 8940HX - (16 GB/1 TB SSD/Windows 11 Home/8 GB Graphics/N...</t>
+  </si>
+  <si>
+    <t>₹1,54,990</t>
+  </si>
+  <si>
+    <t>ASUS Vivobook S14 OLED (2026) AI PC with Office 2024 + M365 Basic*, Copilot+ PC Intel Core Ultra 5 325...</t>
+  </si>
+  <si>
+    <t>₹1,25,990</t>
   </si>
 </sst>
 </file>
@@ -188,7 +323,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -268,100 +403,100 @@
         <v>18</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B22" t="s" s="0">
         <v>3</v>
@@ -369,26 +504,218 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>22</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
